--- a/daily_matches/job_matches_2026-03-06.xlsx
+++ b/daily_matches/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,117 +468,117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Analyst, Risk Data Engineering</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, MLflow, CI/CD, Databricks, Redshift</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, S3, BigQuery, Data Lake, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c054d24fbe757c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0a8c3e1d955c79</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>CCS Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, MLflow, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0daa2739654d2f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Kafka, NoSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=43c7e17e3710a8b4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36669407e627b585</t>
+          <t>https://www.indeed.com/viewjob?jk=815fc66c898092a0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Terraform, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Azure ML, MLflow, Docker, Kubernetes, Databricks, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Gen AI Engineer (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=24193c69942175bf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, EC2, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,252 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Systems</t>
+          <t>Safety Modeling Engineer – Counterfactual &amp; Behavioral Safety Modeling (GPSSC)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2e667884cbb664f</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Safety Modeling Engineer – Collision Severity and Safety Impact Modeling (GPSSC)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c132c8bafc240b9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GenAI Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d21acdf5aa3edec</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Scientist (Data Science)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Everett, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Databricks, Tableau, Power BI, Matplotlib, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27f23ac699145218</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Product Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ALTIMATE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Kubernetes, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer – Distributed Inference</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62f77c01ffbc91c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>General Dynamics Information Technology</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ea11c3a57a7712</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c72aa5ea3e941f5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-06.xlsx
+++ b/daily_matches/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, S3, BigQuery, Data Lake, Dataflow</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0a8c3e1d955c79</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd181016bc08a7a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CCS Inc</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, MLflow, Docker</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0daa2739654d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, Kubernetes</t>
+          <t>Data Scientist, Snowflake, Hadoop, MongoDB, Tableau, Python, SQL, R, Java, Julia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43c7e17e3710a8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Prompt Engineering, S3, Kinesis, Git, Quicksight, Python, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815fc66c898092a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2ee274259b2b0969</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Azure ML, MLflow, Docker, Kubernetes, Databricks, Python</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gen AI Engineer (Remote)</t>
+          <t>Software Engineer III - Backend</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes</t>
+          <t>RAG, Kubernetes, CI/CD, PostgreSQL, Cassandra, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24193c69942175bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e84202aaf2d40639</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>AWS Developer/Integration Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,33 +692,33 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Tableau, Python, SQL</t>
+          <t>RAG, S3, Kinesis, CI/CD, Terraform, Git, Quicksight, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a60d7d509fbceed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Safety Modeling Engineer – Counterfactual &amp; Behavioral Safety Modeling (GPSSC)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,33 +727,33 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e667884cbb664f</t>
+          <t>https://www.indeed.com/viewjob?jk=60b102bc9264a2d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Safety Modeling Engineer – Collision Severity and Safety Impact Modeling (GPSSC)</t>
+          <t>AI Engineer - Senior</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
+          <t>AI Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c132c8bafc240b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e763a514b489fef0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d21acdf5aa3edec</t>
+          <t>https://www.indeed.com/viewjob?jk=74a147899628691c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist (Data Science)</t>
+          <t>Visualization Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Everett, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Databricks, Tableau, Power BI, Matplotlib, Python, SQL</t>
+          <t>CI/CD, Git, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,112 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27f23ac699145218</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Product Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ALTIMATE</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Kubernetes, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer – Distributed Inference</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, LLaMA, Kubernetes, CI/CD, Jenkins, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62f77c01ffbc91c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c72aa5ea3e941f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-06.xlsx
+++ b/daily_matches/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Database Development Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,357 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd181016bc08a7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NetApp</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Data Scientist, Snowflake, Hadoop, MongoDB, Tableau, Python, SQL, R, Java, Julia</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>rockITdata</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, S3, Kinesis, Git, Quicksight, Python, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee274259b2b0969</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Teradata</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Backend</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, PostgreSQL, Cassandra, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e84202aaf2d40639</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AWS Developer/Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>rockITdata</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kinesis, CI/CD, Terraform, Git, Quicksight, Python, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a60d7d509fbceed</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mutual of Omaha</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60b102bc9264a2d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI Engineer - Senior</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e763a514b489fef0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74a147899628691c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Visualization Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
+          <t>https://www.indeed.com/viewjob?jk=0851e8fad5830e58</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-06.xlsx
+++ b/daily_matches/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,700 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Database Development Engineer</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79e35d1cd7a86f17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Senior AI/ ML Engineer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Universal Orlando Resort</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afd2ed25aaffabda</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Data Engineer I (Base Camp)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quorum Business Solutions</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Data Engineer I (Base Camp)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Quorum Business Solutions</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regulatory Compliance Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c43803189a7eb93f</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cloud Posture Management Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=067142cff93a1db8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kubernetes Security Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Hadoop, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ed1c8109ce5f745</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Pinecone, FastAPI, Kubernetes, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=befd26f0914858d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Quantum US</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Centennial, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>11.1</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0851e8fad5830e58</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, Kubernetes, CI/CD, Jenkins, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a43fd8253a10972</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Mistral, Prompt Engineering, CI/CD, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a67ee6e41f0da8e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Security Architecture Consultant</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, Athena, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f45480ebec359b85</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Mistral, Prompt Engineering, CI/CD, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ab95f4a0c794750</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Mistral, Prompt Engineering, CI/CD, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b117bfd993ecd98d</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Junior Frontend Developer (Creative + Full-Stack)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sapphire Media LLC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, FastAPI, Docker, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9d4ded917fb939a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Texas Comptroller of Public Accounts</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Texas Department of Motor Vehicles</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alphanumeric Systems Inc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=653b40c1acf2e03b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Texas Comptroller of Public Accounts</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Data Lake, Dataflow, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Texas Department of Motor Vehicles</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Data Lake, Dataflow, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7682b35bbf97b83a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-06.xlsx
+++ b/daily_matches/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>The Wyanoke Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Thorofare, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python</t>
+          <t>S3, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, SQL, R, Java</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79e35d1cd7a86f17</t>
+          <t>https://www.indeed.com/viewjob?jk=6982bb757f23e348</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI/ ML Engineer</t>
+          <t>AI Application Developer (.NET / Azure AI) - 26-02279</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Copilot, CI/CD, Git, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd2ed25aaffabda</t>
+          <t>https://www.indeed.com/viewjob?jk=1721e503308441b9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>Artificial Intelligence Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>Blue Cross Blue Shield of Michigan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, AWS SageMaker, S3, Redshift, FastAPI, Redshift, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
+          <t>https://www.indeed.com/viewjob?jk=0b223a39487082f8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>Sr. Backend Software Engineer, Fraud Risk Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quorum Business Solutions</t>
+          <t>Navan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f38251c6d8dc24d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Regulatory Compliance Engineer</t>
+          <t>Sr. Backend Software Engineer, Fraud Risk Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Navan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43803189a7eb93f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd3e26ae86e44d1b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Posture Management Engineer</t>
+          <t>Cloud Reliability Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067142cff93a1db8</t>
+          <t>https://www.indeed.com/viewjob?jk=a873ea80c18685a8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Azure Cloud Reliability Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Hadoop, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed1c8109ce5f745</t>
+          <t>https://www.indeed.com/viewjob?jk=6d03be69e8b8b46a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Deployment Engineer</t>
+          <t>Azure Cloud Reliability Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Pinecone, FastAPI, Kubernetes, CI/CD, Python</t>
+          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=befd26f0914858d7</t>
+          <t>https://www.indeed.com/viewjob?jk=3394267006383789</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Cloud Reliability Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quantum US</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Kubernetes, CI/CD, Jenkins, Git, R, Scala</t>
+          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a43fd8253a10972</t>
+          <t>https://www.indeed.com/viewjob?jk=89f67d7a82e1ab2f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Cloud Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Salisbury, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Mistral, Prompt Engineering, CI/CD, R, Java, Scala, Optimization</t>
+          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67ee6e41f0da8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca6b1dc40a2c3ae</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Security Architecture Consultant</t>
+          <t>Azure Cloud Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AHOLD Delhaize</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Athena, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45480ebec359b85</t>
+          <t>https://www.indeed.com/viewjob?jk=7878cfb5b544954f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Research and Data Science Fellow - People &amp; Organization</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Mistral, Prompt Engineering, CI/CD, R, Java, Scala, Optimization</t>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, PySpark, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab95f4a0c794750</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2815420a9c094b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>DLA Piper</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Mistral, Prompt Engineering, CI/CD, R, Java, Scala, Optimization</t>
+          <t>RAG, Synapse, Git, Databricks, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b117bfd993ecd98d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Junior Frontend Developer (Creative + Full-Stack)</t>
+          <t>Senior LLM / Generative AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sapphire Media LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, FastAPI, Docker, Git, MySQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d4ded917fb939a</t>
+          <t>https://www.indeed.com/viewjob?jk=772756a15ab74f19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Data Scientist, AI/ML – Visa Consulting and Analytics</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, Git, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+          <t>https://www.indeed.com/viewjob?jk=de9b1266ec52174f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Visualization Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Heartland Veterinary Partners</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>CI/CD, Git, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,147 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Alphanumeric Systems Inc</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=653b40c1acf2e03b</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Texas Comptroller of Public Accounts</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Data Lake, Dataflow, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Texas Department of Motor Vehicles</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Data Lake, Dataflow, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Agentic AI Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Citizens</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Johnston, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7682b35bbf97b83a</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae96e01998eff74</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-06.xlsx
+++ b/daily_matches/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>Heyer Expectations</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, SQL, R, Java</t>
+          <t>Data Scientist, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6982bb757f23e348</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Application Developer (.NET / Azure AI) - 26-02279</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Copilot, CI/CD, Git, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, YOLO, CI/CD, Git, PySpark, Polars, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1721e503308441b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa6d599d7656f8e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer II</t>
+          <t>Senior AI Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Michigan</t>
+          <t>Fleetpride</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, AWS SageMaker, S3, Redshift, FastAPI, Redshift, Python, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b223a39487082f8</t>
+          <t>https://www.indeed.com/viewjob?jk=6689029748dbcf83</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Backend Software Engineer, Fraud Risk Platform</t>
+          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Navan</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Java</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38251c6d8dc24d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Backend Software Engineer, Fraud Risk Platform</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Navan</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Java</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Polars, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3e26ae86e44d1b</t>
+          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Reliability Engineer III</t>
+          <t>Junior Java Developer (Clearable)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Cassandra, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a873ea80c18685a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0bab8ec5dacaa3f1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Cloud Reliability Engineer III</t>
+          <t>SENIOR JAVA DEVELOPER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d03be69e8b8b46a</t>
+          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Cloud Reliability Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, BigQuery, CI/CD, Jenkins, Terraform, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3394267006383789</t>
+          <t>https://www.indeed.com/viewjob?jk=2be2a3802baaabf6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Reliability Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89f67d7a82e1ab2f</t>
+          <t>https://www.indeed.com/viewjob?jk=eeeacdcfbc54a4cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Salisbury, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca6b1dc40a2c3ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e9dac136df78bdbd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer III</t>
+          <t>Data Engineer I (Base Camp)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AHOLD Delhaize</t>
+          <t>Quorum Software</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7878cfb5b544954f</t>
+          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Research and Data Science Fellow - People &amp; Organization</t>
+          <t>Data Engineer I (Base Camp)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Quorum Software</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, PySpark, Tableau, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2815420a9c094b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Sales Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DLA Piper</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Git, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Azure ML, FastAPI, Docker, Kubernetes, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ec2f40b7c71d98</t>
+          <t>https://www.indeed.com/viewjob?jk=04b515c47e820de8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior LLM / Generative AI Engineer</t>
+          <t>QA Automation Engineer- Nexus HyperFabric- SaaS Team</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772756a15ab74f19</t>
+          <t>https://www.indeed.com/viewjob?jk=1586ca94c7ff43ff</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist, AI/ML – Visa Consulting and Analytics</t>
+          <t>Software Engineer III | Middleware</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Git, Tableau, Python, SQL, R</t>
+          <t>RAG, S3, EC2, FastAPI, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9b1266ec52174f</t>
+          <t>https://www.indeed.com/viewjob?jk=a7379077404b765c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Visualization Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Heartland Veterinary Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,21 +1007,161 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, Terraform, BigQuery, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Recruitinflux Private Solution</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=507b23cdca6f1892</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fabric Data Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Herzing University</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Dataflow, PySpark, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39032eb9aeb52d37</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae96e01998eff74</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, Git, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1587aeecd0400ae</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-06.xlsx
+++ b/daily_matches/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Heyer Expectations</t>
+          <t>Tyndale Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Pipersville, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, BigQuery</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d70b12a632c896</t>
+          <t>https://www.indeed.com/viewjob?jk=5e10d417269b254f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, YOLO, CI/CD, Git, PySpark, Polars, Power BI</t>
+          <t>Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa6d599d7656f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf4803b99637b9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fleetpride</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
+          <t>RAG, Copilot, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6689029748dbcf83</t>
+          <t>https://www.indeed.com/viewjob?jk=3c098dfb66b8f459</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Experience (DevEx)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d246408cc27ef6</t>
+          <t>https://www.indeed.com/viewjob?jk=10b675cae8e307cb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Polars, Python, SQL</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=197006d2fc58f4b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d99f47b2f659f2fb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junior Java Developer (Clearable)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Cassandra, NoSQL, SQL, R</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bab8ec5dacaa3f1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb44ee7cdf82d78f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SENIOR JAVA DEVELOPER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, R</t>
+          <t>Data Scientist, RAG, Synapse, CI/CD, Git, Snowflake, Databricks, Power BI, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29cd522088ef96d7</t>
+          <t>https://www.indeed.com/viewjob?jk=3b238886767794dc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Solutions Consulting Internship Summer 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, CI/CD, Jenkins, Terraform, Git, BigQuery, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2be2a3802baaabf6</t>
+          <t>https://www.indeed.com/viewjob?jk=a71fe058414e25a6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IAM Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, CI/CD, BigQuery, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeeacdcfbc54a4cf</t>
+          <t>https://www.indeed.com/viewjob?jk=08cc966194f3535f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9dac136df78bdbd</t>
+          <t>https://www.indeed.com/viewjob?jk=e73af5a5a2e4c2e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d0977bad9433e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4143de05d54935a7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer I (Base Camp)</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quorum Software</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Collegeville, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5eb975a37e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3578631d411737</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Azure ML, FastAPI, Docker, Kubernetes, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04b515c47e820de8</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e4f820b1c4011</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QA Automation Engineer- Nexus HyperFabric- SaaS Team</t>
+          <t>Language Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1586ca94c7ff43ff</t>
+          <t>https://www.indeed.com/viewjob?jk=de5b03bacfa878ee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III | Middleware</t>
+          <t>Language Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, FastAPI, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7379077404b765c</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd6839fc7be0d7e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Language Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Terraform, BigQuery, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6934f303063d3f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7e6b2e77447869</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Language Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Recruitinflux Private Solution</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=507b23cdca6f1892</t>
+          <t>https://www.indeed.com/viewjob?jk=2622fec333d2c445</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Language Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Herzing University</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Stowe, VT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, PySpark, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7fa69e7ec031f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3fab6803e719e81c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Language Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,42 +1126,1862 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39032eb9aeb52d37</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7d9f827ab26037</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05f511b561b97691</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40d4c8eeecc87129</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23441ba70da50712</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a1373f5c106b354</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cheyenne, WY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b632e4fd4444ab02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb6f6536e398b21b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1067c187e325ef6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Charleston, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=877024c556edff6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a03151ff500cdf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Fargo, ND, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2131d1765d10af76</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=371080640c2230f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3197934fb8d01ab4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7348b12b56c1882</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7670b275473e5cbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70a47eb1335db840</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7ca44e7c39fa0a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29fc0e5afeae441f</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa043d1c8790f71f</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23b24b89c88d45a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc5d03e6b4b10eb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3065c2f3727efab</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b690f9a93e4ce7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67718f239c2176cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a0077503e3ed35e</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9620a579ff7d92cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3846f645ea49bd64</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f07ceb0c06f7bdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4a042801655c2d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff93b9ba9381e79f</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fc117b43228634a</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46ccd80e6f505d34</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c088903d6adcd4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00eca0f5519f8c00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dcdbe5bfa16c0f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Manchester, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a6e4ee187b36afd</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Language Data Scientist</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, spaCy, NLTK, Git, Matplotlib, Seaborn, Python</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=913e359b99d5f08e</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Celebration, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Git, Kafka, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ece4794b980b0cdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sr Business Solutions Data Analyst</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NBCUniversal</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Universal City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>S3, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96b52635fe56ae17</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Kubernetes Security Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Kafka, Hadoop, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a4eab1ccb5d6492</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Compute Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>GSK</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=975599ca2add18c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Compute Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>GSK</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Collegeville, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37eab012690da57c</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Compute Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GSK</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24b371e6b9aabd95</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Compute Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GSK</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f770f71be84a3d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>merican Inc</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8bf5d8094bc57c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Java/Python Software Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Callibrity</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8f1027fa5938949</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Technical Architect - Databricks</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Stitch Consulting Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, CI/CD, Terraform, Git, Databricks, PySpark, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fc456e58c1064f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FINGERPRINT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a7ff3fba41e6d32</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>R&amp;D Software Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>University of Arizona</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tucson, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7747b0c85b8a08d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Machine Learning / Speech Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Elsa Science</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Los Gatos, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, S3, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de0a2e33d67216d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Back-End Engineer, US Remote</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Taxgpt</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, AKS, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27a8f6095fd8db18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AI Application Developer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Copilot, CI/CD, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1171b879be51e22e</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, BigQuery, Git, BigQuery, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1587aeecd0400ae</t>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, Athena, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7150f253f13f6ed0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Development Engineer II - GraphQL Platform</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a143c86297b6cfde</t>
         </is>
       </c>
     </row>
